--- a/data/trans_camb/IP16A07-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A07-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,6</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,1</t>
+          <t>0,0; 19,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,02</t>
+          <t>0,0; 9,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,9</t>
+          <t>0,0; 10,44</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,13</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,77</t>
+          <t>0,0; 36,32</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,39</t>
+          <t>0,0; 18,82</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,48</t>
+          <t>0,31; 3,76</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,8</t>
+          <t>0,16; 1,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A07-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A07-Provincia-trans_camb.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 6,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 4,3</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,9</t>
+          <t>0,0; 16,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,23</t>
+          <t>0,0; 11,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,44</t>
+          <t>0,0; 11,34</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,32</t>
+          <t>0,0; 40,03</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,82</t>
+          <t>0,0; 17,06</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,76</t>
+          <t>0,28; 3,24</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,59</t>
+          <t>0,15; 1,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A07-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A07-Provincia-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero pastillas para dormir</t>
+          <t>Menores que consumieron pastillas para dormir</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>1,06</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,3</t>
+          <t>0,0; 5,32</t>
         </is>
       </c>
     </row>
@@ -956,22 +956,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 14,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,61</t>
+          <t>0,0; 10,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,75</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
     </row>
@@ -2036,22 +2036,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8,79</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>8,56</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>3,38</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 38,49</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,06</t>
+          <t>0,0; 15,93</t>
         </is>
       </c>
     </row>
@@ -2252,22 +2252,22 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2352,24 +2352,24 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>0,45</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,67</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,37; 4,28</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,58</t>
+          <t>0,18; 2,1</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
